--- a/Results/Phase 2/Methanol/methanol resource use fossils results.xlsx
+++ b/Results/Phase 2/Methanol/methanol resource use fossils results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>33.3087529084341</v>
+        <v>32.89877055670665</v>
       </c>
       <c r="C33" t="n">
-        <v>35.70976174875059</v>
+        <v>35.56686432590832</v>
       </c>
       <c r="D33" t="n">
-        <v>33.00879410647106</v>
+        <v>32.69308895700247</v>
       </c>
       <c r="E33" t="n">
-        <v>32.32931007041042</v>
+        <v>32.04180193018766</v>
       </c>
       <c r="F33" t="n">
-        <v>33.03536131390291</v>
+        <v>32.70427344388348</v>
       </c>
       <c r="G33" t="n">
-        <v>33.49631728385476</v>
+        <v>33.00553295676955</v>
       </c>
       <c r="H33" t="n">
-        <v>33.58289898126432</v>
+        <v>33.01438243091227</v>
       </c>
       <c r="I33" t="n">
-        <v>32.91009640751581</v>
+        <v>32.63385693931098</v>
       </c>
       <c r="J33" t="n">
-        <v>33.56196152709877</v>
+        <v>33.03678492267663</v>
       </c>
       <c r="K33" t="n">
-        <v>33.45285673335098</v>
+        <v>32.95385639924246</v>
       </c>
       <c r="L33" t="n">
-        <v>33.80132082673148</v>
+        <v>33.17484692919584</v>
       </c>
       <c r="M33" t="n">
-        <v>34.43600308370912</v>
+        <v>33.5176544024778</v>
       </c>
       <c r="N33" t="n">
-        <v>33.68207914462888</v>
+        <v>33.09492313414852</v>
       </c>
       <c r="O33" t="n">
-        <v>37.76517502070238</v>
+        <v>37.32492729104703</v>
       </c>
       <c r="P33" t="n">
-        <v>33.8040213835885</v>
+        <v>33.19583456306098</v>
       </c>
       <c r="Q33" t="n">
-        <v>33.31667456336309</v>
+        <v>32.87764941141882</v>
       </c>
       <c r="R33" t="n">
-        <v>33.09431308698354</v>
+        <v>32.73800384726427</v>
       </c>
       <c r="S33" t="n">
-        <v>33.45667023840046</v>
+        <v>32.98066567613647</v>
       </c>
       <c r="T33" t="n">
-        <v>33.46534547304706</v>
+        <v>32.95769517691144</v>
       </c>
       <c r="U33" t="n">
-        <v>37.85267327880172</v>
+        <v>37.13799447184093</v>
       </c>
       <c r="V33" t="n">
-        <v>33.3522698117898</v>
+        <v>32.92318686662203</v>
       </c>
       <c r="W33" t="n">
-        <v>40.51380772057611</v>
+        <v>39.76989599792812</v>
       </c>
       <c r="X33" t="n">
-        <v>33.26640817030427</v>
+        <v>32.8462034685943</v>
       </c>
       <c r="Y33" t="n">
-        <v>34.2129771078173</v>
+        <v>33.41598937458961</v>
       </c>
       <c r="Z33" t="n">
-        <v>35.01262574716326</v>
+        <v>34.50167204391825</v>
       </c>
       <c r="AA33" t="n">
-        <v>33.37700561227985</v>
+        <v>32.91828241582829</v>
       </c>
       <c r="AB33" t="n">
-        <v>34.46861366441192</v>
+        <v>33.52044199220175</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.05039942787697</v>
+        <v>32.03335006397042</v>
       </c>
       <c r="C33" t="n">
-        <v>35.25763149609966</v>
+        <v>35.19229885630654</v>
       </c>
       <c r="D33" t="n">
-        <v>32.26794562503726</v>
+        <v>32.1622228170041</v>
       </c>
       <c r="E33" t="n">
-        <v>31.54136247241648</v>
+        <v>31.49317970302054</v>
       </c>
       <c r="F33" t="n">
-        <v>32.47396337791394</v>
+        <v>32.28225553532285</v>
       </c>
       <c r="G33" t="n">
-        <v>32.56922843782324</v>
+        <v>32.35705328450448</v>
       </c>
       <c r="H33" t="n">
-        <v>32.59170484730359</v>
+        <v>32.34476138131815</v>
       </c>
       <c r="I33" t="n">
-        <v>32.2672848557071</v>
+        <v>32.15957024223546</v>
       </c>
       <c r="J33" t="n">
-        <v>32.52266834150921</v>
+        <v>32.32040974823443</v>
       </c>
       <c r="K33" t="n">
-        <v>32.67275111003723</v>
+        <v>32.41592431922643</v>
       </c>
       <c r="L33" t="n">
-        <v>32.42846402155096</v>
+        <v>32.26639291306742</v>
       </c>
       <c r="M33" t="n">
-        <v>32.46203537770266</v>
+        <v>32.27639559435433</v>
       </c>
       <c r="N33" t="n">
-        <v>32.73851803665637</v>
+        <v>32.43733962043056</v>
       </c>
       <c r="O33" t="n">
-        <v>36.65113660502676</v>
+        <v>36.3751800599205</v>
       </c>
       <c r="P33" t="n">
-        <v>33.10424892219369</v>
+        <v>32.68795059251907</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.25381131553853</v>
+        <v>32.15571066002131</v>
       </c>
       <c r="R33" t="n">
-        <v>32.230423982423</v>
+        <v>32.13648908127705</v>
       </c>
       <c r="S33" t="n">
-        <v>32.60154142653812</v>
+        <v>32.37504001969381</v>
       </c>
       <c r="T33" t="n">
-        <v>32.62946563240522</v>
+        <v>32.37078248446418</v>
       </c>
       <c r="U33" t="n">
-        <v>36.16345852576393</v>
+        <v>35.91890042947411</v>
       </c>
       <c r="V33" t="n">
-        <v>32.35148016519072</v>
+        <v>32.22022009260572</v>
       </c>
       <c r="W33" t="n">
-        <v>39.24928456334224</v>
+        <v>38.78461705782851</v>
       </c>
       <c r="X33" t="n">
-        <v>33.13529420869932</v>
+        <v>32.68409603284451</v>
       </c>
       <c r="Y33" t="n">
-        <v>33.02689199955998</v>
+        <v>32.60945602926113</v>
       </c>
       <c r="Z33" t="n">
-        <v>33.40669793212219</v>
+        <v>33.30677818459924</v>
       </c>
       <c r="AA33" t="n">
-        <v>32.92859707126081</v>
+        <v>32.55243220947862</v>
       </c>
       <c r="AB33" t="n">
-        <v>32.49685785934101</v>
+        <v>32.28992458108719</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>33.0599290535473</v>
+        <v>32.73381357537159</v>
       </c>
       <c r="C33" t="n">
-        <v>35.6368138939244</v>
+        <v>35.50986075047472</v>
       </c>
       <c r="D33" t="n">
-        <v>33.05583977776345</v>
+        <v>32.70549898354688</v>
       </c>
       <c r="E33" t="n">
-        <v>32.27978214732536</v>
+        <v>32.0016369982734</v>
       </c>
       <c r="F33" t="n">
-        <v>32.86642936601027</v>
+        <v>32.59483141646498</v>
       </c>
       <c r="G33" t="n">
-        <v>33.38640092314709</v>
+        <v>32.92734875336338</v>
       </c>
       <c r="H33" t="n">
-        <v>33.35661177359554</v>
+        <v>32.87062854223816</v>
       </c>
       <c r="I33" t="n">
-        <v>32.83863097702631</v>
+        <v>32.57738537154415</v>
       </c>
       <c r="J33" t="n">
-        <v>33.4420472358778</v>
+        <v>32.95163341410279</v>
       </c>
       <c r="K33" t="n">
-        <v>33.18621302934913</v>
+        <v>32.79791687900855</v>
       </c>
       <c r="L33" t="n">
-        <v>33.56942164449972</v>
+        <v>33.02230408217093</v>
       </c>
       <c r="M33" t="n">
-        <v>34.19445141730918</v>
+        <v>33.36506100067959</v>
       </c>
       <c r="N33" t="n">
-        <v>33.52588397540218</v>
+        <v>32.98827708621608</v>
       </c>
       <c r="O33" t="n">
-        <v>37.71592888538236</v>
+        <v>37.2663548728483</v>
       </c>
       <c r="P33" t="n">
-        <v>33.78736311087529</v>
+        <v>33.17262823032906</v>
       </c>
       <c r="Q33" t="n">
-        <v>33.17478444392318</v>
+        <v>32.78074114094965</v>
       </c>
       <c r="R33" t="n">
-        <v>33.12919398690934</v>
+        <v>32.74292344515852</v>
       </c>
       <c r="S33" t="n">
-        <v>33.31448435248087</v>
+        <v>32.88293359345278</v>
       </c>
       <c r="T33" t="n">
-        <v>33.20248971381816</v>
+        <v>32.79115527673562</v>
       </c>
       <c r="U33" t="n">
-        <v>37.55122109518344</v>
+        <v>36.92441164458314</v>
       </c>
       <c r="V33" t="n">
-        <v>33.20061802389331</v>
+        <v>32.82486586163092</v>
       </c>
       <c r="W33" t="n">
-        <v>40.47765152019734</v>
+        <v>39.71370769685127</v>
       </c>
       <c r="X33" t="n">
-        <v>33.2794107926388</v>
+        <v>32.8401541325681</v>
       </c>
       <c r="Y33" t="n">
-        <v>34.14050250820148</v>
+        <v>33.36326106989048</v>
       </c>
       <c r="Z33" t="n">
-        <v>34.75998477185549</v>
+        <v>34.31620120231833</v>
       </c>
       <c r="AA33" t="n">
-        <v>33.16647411305996</v>
+        <v>32.78084224723928</v>
       </c>
       <c r="AB33" t="n">
-        <v>34.36596336147066</v>
+        <v>33.44600153948932</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.86024529149827</v>
+        <v>32.59192228018358</v>
       </c>
       <c r="C33" t="n">
-        <v>35.71613717499498</v>
+        <v>35.53877716045684</v>
       </c>
       <c r="D33" t="n">
-        <v>33.13713635441735</v>
+        <v>32.73662855644879</v>
       </c>
       <c r="E33" t="n">
-        <v>32.14568316339449</v>
+        <v>31.90723626396689</v>
       </c>
       <c r="F33" t="n">
-        <v>32.84125230922878</v>
+        <v>32.5641409732979</v>
       </c>
       <c r="G33" t="n">
-        <v>33.26967906459308</v>
+        <v>32.843253371321</v>
       </c>
       <c r="H33" t="n">
-        <v>33.21513658938134</v>
+        <v>32.76930366581347</v>
       </c>
       <c r="I33" t="n">
-        <v>32.88687407409427</v>
+        <v>32.58759788053148</v>
       </c>
       <c r="J33" t="n">
-        <v>33.30179172331361</v>
+        <v>32.85146985671381</v>
       </c>
       <c r="K33" t="n">
-        <v>32.8793039054551</v>
+        <v>32.60332875149548</v>
       </c>
       <c r="L33" t="n">
-        <v>33.34544829474149</v>
+        <v>32.87263556483207</v>
       </c>
       <c r="M33" t="n">
-        <v>33.9476546941405</v>
+        <v>33.20277305669008</v>
       </c>
       <c r="N33" t="n">
-        <v>33.21343692066965</v>
+        <v>32.785815861551</v>
       </c>
       <c r="O33" t="n">
-        <v>37.51543100084786</v>
+        <v>37.08857084287941</v>
       </c>
       <c r="P33" t="n">
-        <v>33.67298145861974</v>
+        <v>33.09014385566833</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.98605043738989</v>
+        <v>32.65556675328903</v>
       </c>
       <c r="R33" t="n">
-        <v>32.97262346950401</v>
+        <v>32.63419037528799</v>
       </c>
       <c r="S33" t="n">
-        <v>33.18749920467458</v>
+        <v>32.79071975891736</v>
       </c>
       <c r="T33" t="n">
-        <v>33.15287169492044</v>
+        <v>32.74351954087383</v>
       </c>
       <c r="U33" t="n">
-        <v>37.12737466627839</v>
+        <v>36.62158736280451</v>
       </c>
       <c r="V33" t="n">
-        <v>33.11400393379679</v>
+        <v>32.75758986789194</v>
       </c>
       <c r="W33" t="n">
-        <v>40.18381257609334</v>
+        <v>39.48245969885617</v>
       </c>
       <c r="X33" t="n">
-        <v>33.41362808800211</v>
+        <v>32.90217668359181</v>
       </c>
       <c r="Y33" t="n">
-        <v>34.05488149800548</v>
+        <v>33.29335545227398</v>
       </c>
       <c r="Z33" t="n">
-        <v>34.462582720344</v>
+        <v>34.10355382066759</v>
       </c>
       <c r="AA33" t="n">
-        <v>33.10174674945684</v>
+        <v>32.72411376774679</v>
       </c>
       <c r="AB33" t="n">
-        <v>34.18125130132859</v>
+        <v>33.32002043262909</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.76421946004136</v>
+        <v>32.52335646609292</v>
       </c>
       <c r="C33" t="n">
-        <v>35.69298582146105</v>
+        <v>35.50739657914058</v>
       </c>
       <c r="D33" t="n">
-        <v>32.86626855750858</v>
+        <v>32.56962891289427</v>
       </c>
       <c r="E33" t="n">
-        <v>31.84367828927749</v>
+        <v>31.71784105681402</v>
       </c>
       <c r="F33" t="n">
-        <v>32.99502013088435</v>
+        <v>32.64050430959243</v>
       </c>
       <c r="G33" t="n">
-        <v>33.13519700194949</v>
+        <v>32.75421015981784</v>
       </c>
       <c r="H33" t="n">
-        <v>33.10646696769781</v>
+        <v>32.69062160662703</v>
       </c>
       <c r="I33" t="n">
-        <v>32.99199455983882</v>
+        <v>32.63652822148419</v>
       </c>
       <c r="J33" t="n">
-        <v>33.18234662593943</v>
+        <v>32.76874929946298</v>
       </c>
       <c r="K33" t="n">
-        <v>33.11164694653072</v>
+        <v>32.73086687954635</v>
       </c>
       <c r="L33" t="n">
-        <v>33.30686084143269</v>
+        <v>32.84502780546044</v>
       </c>
       <c r="M33" t="n">
-        <v>33.72846238602325</v>
+        <v>33.07543707470722</v>
       </c>
       <c r="N33" t="n">
-        <v>33.05887758874955</v>
+        <v>32.6790051075908</v>
       </c>
       <c r="O33" t="n">
-        <v>37.15519964969778</v>
+        <v>36.80580333513184</v>
       </c>
       <c r="P33" t="n">
-        <v>33.45364307334584</v>
+        <v>32.95202382387999</v>
       </c>
       <c r="Q33" t="n">
-        <v>33.02871398367023</v>
+        <v>32.67099035450673</v>
       </c>
       <c r="R33" t="n">
-        <v>32.99040584014507</v>
+        <v>32.62877347947029</v>
       </c>
       <c r="S33" t="n">
-        <v>33.20867390181729</v>
+        <v>32.79248188732765</v>
       </c>
       <c r="T33" t="n">
-        <v>33.17436080825311</v>
+        <v>32.74028038151155</v>
       </c>
       <c r="U33" t="n">
-        <v>36.94347151411689</v>
+        <v>36.48244173184838</v>
       </c>
       <c r="V33" t="n">
-        <v>33.00291901029532</v>
+        <v>32.67639275546247</v>
       </c>
       <c r="W33" t="n">
-        <v>39.98650664057441</v>
+        <v>39.32289901907931</v>
       </c>
       <c r="X33" t="n">
-        <v>33.42233427456623</v>
+        <v>32.90110072551693</v>
       </c>
       <c r="Y33" t="n">
-        <v>33.86432348447917</v>
+        <v>33.1571682129007</v>
       </c>
       <c r="Z33" t="n">
-        <v>34.07640034739629</v>
+        <v>33.82397009034124</v>
       </c>
       <c r="AA33" t="n">
-        <v>33.1540903479411</v>
+        <v>32.73882895252891</v>
       </c>
       <c r="AB33" t="n">
-        <v>33.95214379327489</v>
+        <v>33.17929879785361</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.29663860382907</v>
+        <v>32.22216693536668</v>
       </c>
       <c r="C33" t="n">
-        <v>35.29968592278382</v>
+        <v>35.25497588950705</v>
       </c>
       <c r="D33" t="n">
-        <v>32.43951563749796</v>
+        <v>32.30042521807319</v>
       </c>
       <c r="E33" t="n">
-        <v>31.99810908999033</v>
+        <v>31.79576683480767</v>
       </c>
       <c r="F33" t="n">
-        <v>32.3473639886971</v>
+        <v>32.24648313264981</v>
       </c>
       <c r="G33" t="n">
-        <v>32.74152749631405</v>
+        <v>32.504387196315</v>
       </c>
       <c r="H33" t="n">
-        <v>32.76431121942392</v>
+        <v>32.48319325146976</v>
       </c>
       <c r="I33" t="n">
-        <v>32.48091571838519</v>
+        <v>32.32340522222467</v>
       </c>
       <c r="J33" t="n">
-        <v>32.88110038262705</v>
+        <v>32.57998407892585</v>
       </c>
       <c r="K33" t="n">
-        <v>32.63984283886151</v>
+        <v>32.42863918449493</v>
       </c>
       <c r="L33" t="n">
-        <v>32.74749612305961</v>
+        <v>32.50423706689057</v>
       </c>
       <c r="M33" t="n">
-        <v>33.02410737914326</v>
+        <v>32.65904855602376</v>
       </c>
       <c r="N33" t="n">
-        <v>33.16987523574569</v>
+        <v>32.73968940371503</v>
       </c>
       <c r="O33" t="n">
-        <v>37.27347874693652</v>
+        <v>36.87215778189786</v>
       </c>
       <c r="P33" t="n">
-        <v>33.53328527384553</v>
+        <v>32.97710082153352</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.70877990111189</v>
+        <v>32.46641327001903</v>
       </c>
       <c r="R33" t="n">
-        <v>32.5160345143034</v>
+        <v>32.34153984659109</v>
       </c>
       <c r="S33" t="n">
-        <v>32.61431216671109</v>
+        <v>32.42849970028281</v>
       </c>
       <c r="T33" t="n">
-        <v>32.84128684729025</v>
+        <v>32.54210297051133</v>
       </c>
       <c r="U33" t="n">
-        <v>36.88029608884889</v>
+        <v>36.44428025836935</v>
       </c>
       <c r="V33" t="n">
-        <v>32.91921517350709</v>
+        <v>32.60866418318429</v>
       </c>
       <c r="W33" t="n">
-        <v>40.45477477556816</v>
+        <v>39.61239650343304</v>
       </c>
       <c r="X33" t="n">
-        <v>32.78990801775173</v>
+        <v>32.50783639688763</v>
       </c>
       <c r="Y33" t="n">
-        <v>33.77319074398221</v>
+        <v>33.09958873304404</v>
       </c>
       <c r="Z33" t="n">
-        <v>34.14252049752891</v>
+        <v>33.85847673306294</v>
       </c>
       <c r="AA33" t="n">
-        <v>32.79195912586206</v>
+        <v>32.51263518950399</v>
       </c>
       <c r="AB33" t="n">
-        <v>33.379399083316</v>
+        <v>32.84500910481245</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.07236853527959</v>
+        <v>32.05028974955887</v>
       </c>
       <c r="C33" t="n">
-        <v>35.24914206639376</v>
+        <v>35.18956786261902</v>
       </c>
       <c r="D33" t="n">
-        <v>32.12711785859271</v>
+        <v>32.08196672044702</v>
       </c>
       <c r="E33" t="n">
-        <v>31.6148147015647</v>
+        <v>31.53812175235751</v>
       </c>
       <c r="F33" t="n">
-        <v>32.29370772716868</v>
+        <v>32.1803220831971</v>
       </c>
       <c r="G33" t="n">
-        <v>32.53953868560275</v>
+        <v>32.34834698575101</v>
       </c>
       <c r="H33" t="n">
-        <v>32.55392054672073</v>
+        <v>32.32661899689224</v>
       </c>
       <c r="I33" t="n">
-        <v>32.28211130915891</v>
+        <v>32.17250149006915</v>
       </c>
       <c r="J33" t="n">
-        <v>32.53133225394172</v>
+        <v>32.33449199685666</v>
       </c>
       <c r="K33" t="n">
-        <v>32.22639055205254</v>
+        <v>32.1439451604333</v>
       </c>
       <c r="L33" t="n">
-        <v>32.12009591938673</v>
+        <v>32.08091931683626</v>
       </c>
       <c r="M33" t="n">
-        <v>32.38862428275137</v>
+        <v>32.24546259744869</v>
       </c>
       <c r="N33" t="n">
-        <v>32.81870656854977</v>
+        <v>32.49854546173076</v>
       </c>
       <c r="O33" t="n">
-        <v>36.89099197425846</v>
+        <v>36.54647164785337</v>
       </c>
       <c r="P33" t="n">
-        <v>33.23823071536595</v>
+        <v>32.76746186739625</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.27988134868946</v>
+        <v>32.17881311946751</v>
       </c>
       <c r="R33" t="n">
-        <v>32.17046982048388</v>
+        <v>32.1059564693106</v>
       </c>
       <c r="S33" t="n">
-        <v>32.35983616847275</v>
+        <v>32.23357160853753</v>
       </c>
       <c r="T33" t="n">
-        <v>32.51263197481177</v>
+        <v>32.31389863609399</v>
       </c>
       <c r="U33" t="n">
-        <v>36.07970661049273</v>
+        <v>35.88092819287792</v>
       </c>
       <c r="V33" t="n">
-        <v>32.60819033422899</v>
+        <v>32.38591222992</v>
       </c>
       <c r="W33" t="n">
-        <v>39.40719518412947</v>
+        <v>38.90437478789542</v>
       </c>
       <c r="X33" t="n">
-        <v>33.01590104579954</v>
+        <v>32.61831790383322</v>
       </c>
       <c r="Y33" t="n">
-        <v>33.35747389863747</v>
+        <v>32.81244903240675</v>
       </c>
       <c r="Z33" t="n">
-        <v>33.50695834012878</v>
+        <v>33.37858089654411</v>
       </c>
       <c r="AA33" t="n">
-        <v>32.81292800961688</v>
+        <v>32.48955780399529</v>
       </c>
       <c r="AB33" t="n">
-        <v>32.81610740083006</v>
+        <v>32.48874822046773</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.02128030309318</v>
+        <v>32.00005437304097</v>
       </c>
       <c r="C33" t="n">
-        <v>35.15524636081207</v>
+        <v>35.11153525372022</v>
       </c>
       <c r="D33" t="n">
-        <v>32.15438480959577</v>
+        <v>32.07813753243086</v>
       </c>
       <c r="E33" t="n">
-        <v>31.4451907820879</v>
+        <v>31.42138689176868</v>
       </c>
       <c r="F33" t="n">
-        <v>32.3682990122976</v>
+        <v>32.2023741530725</v>
       </c>
       <c r="G33" t="n">
-        <v>32.2817097898874</v>
+        <v>32.16287749250639</v>
       </c>
       <c r="H33" t="n">
-        <v>32.48401954210879</v>
+        <v>32.26661939583327</v>
       </c>
       <c r="I33" t="n">
-        <v>32.21032685375248</v>
+        <v>32.10948946923914</v>
       </c>
       <c r="J33" t="n">
-        <v>32.35034710780804</v>
+        <v>32.1999761680561</v>
       </c>
       <c r="K33" t="n">
-        <v>32.20393252612748</v>
+        <v>32.10944582891019</v>
       </c>
       <c r="L33" t="n">
-        <v>32.09196954464483</v>
+        <v>32.04447607078174</v>
       </c>
       <c r="M33" t="n">
-        <v>32.3472699155077</v>
+        <v>32.19407347753582</v>
       </c>
       <c r="N33" t="n">
-        <v>32.5294512059783</v>
+        <v>32.30209965300527</v>
       </c>
       <c r="O33" t="n">
-        <v>36.50251715500977</v>
+        <v>36.24183891895531</v>
       </c>
       <c r="P33" t="n">
-        <v>33.02481903744567</v>
+        <v>32.62397384384758</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.15394740133519</v>
+        <v>32.07988911149052</v>
       </c>
       <c r="R33" t="n">
-        <v>32.10437380465644</v>
+        <v>32.04669290404501</v>
       </c>
       <c r="S33" t="n">
-        <v>32.44061129877205</v>
+        <v>32.26073886824862</v>
       </c>
       <c r="T33" t="n">
-        <v>32.42048278599194</v>
+        <v>32.23519006247591</v>
       </c>
       <c r="U33" t="n">
-        <v>35.9621362352154</v>
+        <v>35.75607065840961</v>
       </c>
       <c r="V33" t="n">
-        <v>32.38168123763356</v>
+        <v>32.22353510031112</v>
       </c>
       <c r="W33" t="n">
-        <v>38.74942388241069</v>
+        <v>38.44457076188329</v>
       </c>
       <c r="X33" t="n">
-        <v>33.05796547097655</v>
+        <v>32.62798114193515</v>
       </c>
       <c r="Y33" t="n">
-        <v>32.91487684038868</v>
+        <v>32.52689775473882</v>
       </c>
       <c r="Z33" t="n">
-        <v>33.22526728093347</v>
+        <v>33.16370586105061</v>
       </c>
       <c r="AA33" t="n">
-        <v>32.81660619875841</v>
+        <v>32.47106480920998</v>
       </c>
       <c r="AB33" t="n">
-        <v>32.66144535571869</v>
+        <v>32.37064916875468</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.75258970225931</v>
+        <v>32.53269186263464</v>
       </c>
       <c r="C33" t="n">
-        <v>35.45893579555155</v>
+        <v>35.38856783181619</v>
       </c>
       <c r="D33" t="n">
-        <v>32.78651110661141</v>
+        <v>32.53426669093233</v>
       </c>
       <c r="E33" t="n">
-        <v>32.15765749312622</v>
+        <v>31.91701501486583</v>
       </c>
       <c r="F33" t="n">
-        <v>32.60086893116352</v>
+        <v>32.42694298296622</v>
       </c>
       <c r="G33" t="n">
-        <v>33.29579974285815</v>
+        <v>32.86969906193873</v>
       </c>
       <c r="H33" t="n">
-        <v>33.20383746994834</v>
+        <v>32.76862642446682</v>
       </c>
       <c r="I33" t="n">
-        <v>32.74031926755613</v>
+        <v>32.50726439623693</v>
       </c>
       <c r="J33" t="n">
-        <v>33.28849644346976</v>
+        <v>32.85436795618502</v>
       </c>
       <c r="K33" t="n">
-        <v>32.87694124869353</v>
+        <v>32.60392958439558</v>
       </c>
       <c r="L33" t="n">
-        <v>33.36539721324635</v>
+        <v>32.89646743849359</v>
       </c>
       <c r="M33" t="n">
-        <v>34.04065116840267</v>
+        <v>33.29582891725791</v>
       </c>
       <c r="N33" t="n">
-        <v>33.29058890833578</v>
+        <v>32.8356962483532</v>
       </c>
       <c r="O33" t="n">
-        <v>37.42347698855252</v>
+        <v>37.03713994356472</v>
       </c>
       <c r="P33" t="n">
-        <v>33.60005960223933</v>
+        <v>33.04549078372724</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.8977795944928</v>
+        <v>32.60742725846018</v>
       </c>
       <c r="R33" t="n">
-        <v>32.87498678794296</v>
+        <v>32.58176365835285</v>
       </c>
       <c r="S33" t="n">
-        <v>32.98817586123487</v>
+        <v>32.6828826230506</v>
       </c>
       <c r="T33" t="n">
-        <v>32.95847469200418</v>
+        <v>32.63475475048034</v>
       </c>
       <c r="U33" t="n">
-        <v>37.28905333041729</v>
+        <v>36.73710592939631</v>
       </c>
       <c r="V33" t="n">
-        <v>33.12974947964467</v>
+        <v>32.7687336980302</v>
       </c>
       <c r="W33" t="n">
-        <v>40.43831168002944</v>
+        <v>39.65697945130137</v>
       </c>
       <c r="X33" t="n">
-        <v>33.18302630589132</v>
+        <v>32.76952894511869</v>
       </c>
       <c r="Y33" t="n">
-        <v>34.07962765267919</v>
+        <v>33.31441524606538</v>
       </c>
       <c r="Z33" t="n">
-        <v>34.55514839548539</v>
+        <v>34.16569387898608</v>
       </c>
       <c r="AA33" t="n">
-        <v>33.04578437261305</v>
+        <v>32.69538448354724</v>
       </c>
       <c r="AB33" t="n">
-        <v>34.12402961361484</v>
+        <v>33.29456149356614</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32.14800556524386</v>
+        <v>32.11900768175231</v>
       </c>
       <c r="C33" t="n">
-        <v>35.31285023481854</v>
+        <v>35.25337133797905</v>
       </c>
       <c r="D33" t="n">
-        <v>32.31558404008032</v>
+        <v>32.21630235265741</v>
       </c>
       <c r="E33" t="n">
-        <v>31.81323981537126</v>
+        <v>31.67646617533983</v>
       </c>
       <c r="F33" t="n">
-        <v>32.35042947183011</v>
+        <v>32.23675328521205</v>
       </c>
       <c r="G33" t="n">
-        <v>33.0315293534014</v>
+        <v>32.67386641531257</v>
       </c>
       <c r="H33" t="n">
-        <v>32.92136348759903</v>
+        <v>32.55879316258026</v>
       </c>
       <c r="I33" t="n">
-        <v>32.27924683619263</v>
+        <v>32.19336576363482</v>
       </c>
       <c r="J33" t="n">
-        <v>32.79658082631411</v>
+        <v>32.51675917611308</v>
       </c>
       <c r="K33" t="n">
-        <v>32.48315240811091</v>
+        <v>32.32430696611199</v>
       </c>
       <c r="L33" t="n">
-        <v>32.48678381654819</v>
+        <v>32.32804284339734</v>
       </c>
       <c r="M33" t="n">
-        <v>32.77951214399444</v>
+        <v>32.49934763905592</v>
       </c>
       <c r="N33" t="n">
-        <v>32.86125575938424</v>
+        <v>32.53764765115879</v>
       </c>
       <c r="O33" t="n">
-        <v>36.97959567211121</v>
+        <v>36.6491118715025</v>
       </c>
       <c r="P33" t="n">
-        <v>33.31064744010239</v>
+        <v>32.83404025907006</v>
       </c>
       <c r="Q33" t="n">
-        <v>32.45066627394505</v>
+        <v>32.30346783581204</v>
       </c>
       <c r="R33" t="n">
-        <v>32.32484478341087</v>
+        <v>32.2189194033913</v>
       </c>
       <c r="S33" t="n">
-        <v>32.45127073404417</v>
+        <v>32.30858718636451</v>
       </c>
       <c r="T33" t="n">
-        <v>32.59343311380003</v>
+        <v>32.37812086880812</v>
       </c>
       <c r="U33" t="n">
-        <v>36.42469976313971</v>
+        <v>36.13240416522758</v>
       </c>
       <c r="V33" t="n">
-        <v>32.68404375794582</v>
+        <v>32.45339796488966</v>
       </c>
       <c r="W33" t="n">
-        <v>39.76433091421053</v>
+        <v>39.15412117611805</v>
       </c>
       <c r="X33" t="n">
-        <v>33.10456966988368</v>
+        <v>32.68626281796993</v>
       </c>
       <c r="Y33" t="n">
-        <v>33.86200908694196</v>
+        <v>33.13973209361213</v>
       </c>
       <c r="Z33" t="n">
-        <v>33.7070390551504</v>
+        <v>33.54362147873835</v>
       </c>
       <c r="AA33" t="n">
-        <v>32.64521316071876</v>
+        <v>32.41295221737598</v>
       </c>
       <c r="AB33" t="n">
-        <v>33.56813906866186</v>
+        <v>32.93771876726238</v>
       </c>
     </row>
   </sheetData>
